--- a/excel/Questions.xlsx
+++ b/excel/Questions.xlsx
@@ -1,20 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{93AAFAFE-6224-4079-9EFF-E3650CE23F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1216869B-5062-4648-A51B-5F2E36A9D822}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:1_{93AAFAFE-6224-4079-9EFF-E3650CE23F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6042DAE4-E8E7-42AA-8A37-048A6F826170}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5970" yWindow="2700" windowWidth="21600" windowHeight="11295" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="1" r:id="rId1"/>
-    <sheet name="Q1 - 5s" sheetId="2" r:id="rId2"/>
-    <sheet name="Q2 - 10s" sheetId="3" r:id="rId3"/>
-    <sheet name="Q3 - 15s" sheetId="4" r:id="rId4"/>
-    <sheet name="Q4 - 20s" sheetId="5" r:id="rId5"/>
-    <sheet name="Q5 - 25s" sheetId="6" r:id="rId6"/>
-    <sheet name="Q6 - 31s" sheetId="7" r:id="rId7"/>
+    <sheet name="Item 1a LOC" sheetId="2" r:id="rId2"/>
+    <sheet name="1b LOC Q" sheetId="3" r:id="rId3"/>
+    <sheet name="1c LOC Commands" sheetId="4" r:id="rId4"/>
+    <sheet name="2 Best Gaze" sheetId="5" r:id="rId5"/>
+    <sheet name="3 Visual" sheetId="6" r:id="rId6"/>
+    <sheet name="4 Facial Palsy" sheetId="9" r:id="rId7"/>
+    <sheet name="5 Motor Arm" sheetId="10" r:id="rId8"/>
+    <sheet name="6 Motor Leg" sheetId="12" r:id="rId9"/>
+    <sheet name="7 Limb Ataxia" sheetId="13" r:id="rId10"/>
+    <sheet name="8 Sensory" sheetId="14" r:id="rId11"/>
+    <sheet name="9 Best Language" sheetId="15" r:id="rId12"/>
+    <sheet name="10 Dysarthria" sheetId="17" r:id="rId13"/>
+    <sheet name="11 Extinction and Inattention" sheetId="18" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="91">
   <si>
     <t>Questions Database</t>
   </si>
@@ -114,9 +121,6 @@
     <t>Time when question pop-ups:</t>
   </si>
   <si>
-    <t>5 sec</t>
-  </si>
-  <si>
     <t>Option</t>
   </si>
   <si>
@@ -147,7 +151,23 @@
     <t>1</t>
   </si>
   <si>
-    <t>Not Alert; but arousable by minor stimulation to obey, answer, or respond.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Not Alert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; but arousable by minor stimulation to obey, answer, or respond.</t>
+    </r>
   </si>
   <si>
     <t>FALSE</t>
@@ -159,7 +179,23 @@
     <t>2</t>
   </si>
   <si>
-    <t>Not Alert; requires repeated stimulation to attend, or is obtunded and requires strong or painful.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Not Alert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; requires repeated stimulation to attend, or is obtunded and requires strong or painful.</t>
+    </r>
   </si>
   <si>
     <t>3</t>
@@ -168,26 +204,659 @@
     <t>Responds only with reflex motor or autonomic effects, or totally unresponsive, flaccid, and areflexic.</t>
   </si>
   <si>
-    <t>10 sec</t>
-  </si>
-  <si>
-    <t>15 sec</t>
-  </si>
-  <si>
-    <t>20 sec</t>
-  </si>
-  <si>
-    <t>25 sec</t>
-  </si>
-  <si>
-    <t>31 sec</t>
+    <t>Answers both questions correctly</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Answers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> one question correctly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Answers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> neither question correctly</t>
+    </r>
+  </si>
+  <si>
+    <t>Performs both tasks correctly</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Performs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> one task correctly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Performs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> neither task correctly</t>
+    </r>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Partial gaze palsy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; gaze is abnormal in one or both eyes, but forced deviation or total gaze paresis is not present.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Forced deviation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>, or total gaze paresis is not overcome by the oculocephalic maneuver.</t>
+    </r>
+  </si>
+  <si>
+    <t>No visual loss</t>
+  </si>
+  <si>
+    <t>Partial hemianopia.</t>
+  </si>
+  <si>
+    <t>Complete hemianopia.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Bilaterial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>hemianopia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> (blind including cortical blindness)</t>
+    </r>
+  </si>
+  <si>
+    <t>Normal symmetrical movements.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Minor paralysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> (flattened nasolabial fold, asymmetry on smiling).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Partial paralysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> (total or near-total paralysis of lower face).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Complete paralysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> of one or both sides (absences of facial movement in the upper and lower face).</t>
+    </r>
+  </si>
+  <si>
+    <t>No drift; limb holds 90 (or 45) degrees for full 10 seconds.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Drift</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; limb holds 90 (or 45) degrees, but drifts down before full 10 seconds; does not hit bed or other support.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">There was a slight drift in the right arm. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Some effort against gravity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; limb cannot get to or maintain (if cued) 90 (or 45) degrees, drifts down to bed, but has some effort against gravity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>No effort against gravity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; limb falls</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No movement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Amputation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or joint fusion</t>
+    </r>
+  </si>
+  <si>
+    <t>No drift; leg holds 30-degree position for full 5 seconds.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Drift</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; leg falls by the end of the 5-second period but does not hit the bed.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">There was a slight drift in the right leg. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Some effort against gravity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; leg falls to bed by 5 seconds but has some effort against gravity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>No effort against gravity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">; leg falls to bed immediately. </t>
+    </r>
+  </si>
+  <si>
+    <t>No movement.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Amputation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> or joint fusion</t>
+    </r>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>Present in one limb</t>
+  </si>
+  <si>
+    <t>Present in two limbs</t>
+  </si>
+  <si>
+    <t>Normal; no sensory loss</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mild-to-moderate sensory loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; patient feels pinprick is less sharp or is dull on the affected side; or there is a loss of superficial pain with pinprick, but the patient is aware of being touched.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Severe or total sensory loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">; patient is not aware of being touched in the face, arm, and leg. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">No aphasia; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>normal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mild-to-moderate aphasia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">; some obviousl loss of fluency or facility to comprehension, without signifant limitation on ideas expressed or form of expression. Reduction of speech and/or comprehension, however, makes conversation about provided materials difficult or impossible. For example, in conversation about provided materials, examiner can identify picture or naming card content from patient's response. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Severe aphasia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">; all communication is through fragmentary expression; great need for inference, questioning, and guessing by the listener. Range of information that can be exchanged is limited; listener carries burden of communication. Examiner cannot identify materials provided from patient response. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mute, global aphasia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; no usable speech or auditory comprehension.</t>
+    </r>
+  </si>
+  <si>
+    <t>Normal.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Mild-to-moderate dysarthria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; patietn slurs at least some words and, at worst, can be understood with some difficulty.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Severe dysarthria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>; patient's speech is so slurred as to be unintelligible in the absence of or out of proportion to any dysphagia, or is mute/anarthric.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Intubated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> or other physical barrier</t>
+    </r>
+  </si>
+  <si>
+    <t>No abnormality.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Visual, tactile, auditory, spatial, or personal inattention</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, or extinction to bilateral simultaneous stimulation in one of the sensory modalities. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Profound hemi-inattention or extinction to more than one modality</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">; does not recovntize own hand or orients to only one side of space. </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,6 +922,26 @@
       <color rgb="FFC10E21"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -292,7 +981,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -315,11 +1004,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -348,9 +1065,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -375,14 +1089,34 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -399,6 +1133,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -724,22 +1462,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="48" customHeight="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:3" ht="8.1" customHeight="1"/>
-    <row r="3" spans="1:3" ht="26.1" customHeight="1">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+    </row>
+    <row r="2" spans="1:3" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -747,8 +1485,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:3" ht="21.95" customHeight="1">
+    <row r="4" spans="1:3" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -756,7 +1494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.95" customHeight="1">
+    <row r="6" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -764,7 +1502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.95" customHeight="1">
+    <row r="7" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
@@ -772,7 +1510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.95" customHeight="1">
+    <row r="8" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -780,7 +1518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.95" customHeight="1">
+    <row r="9" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
@@ -788,14 +1526,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="26.1" customHeight="1">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -806,7 +1544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>1</v>
       </c>
@@ -817,7 +1555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2</v>
       </c>
@@ -828,7 +1566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>3</v>
       </c>
@@ -839,7 +1577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>4</v>
       </c>
@@ -850,7 +1588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>5</v>
       </c>
@@ -861,7 +1599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>6</v>
       </c>
@@ -882,10 +1620,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C729A8D9-F257-47F1-855B-AB0D86288958}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
@@ -893,108 +1631,658 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="25">
+        <v>0.19587962962962963</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="4" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="B6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59926F48-CCBB-4DBD-959F-369A75807AE1}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.22725694444444444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6925CF0-4121-4C18-A8B9-DFEF113BD459}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.28545138888888888</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA3C73A-9729-4646-B7DF-8FEA01F81700}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.29726851851851854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC555C62-563F-48EA-A731-9570DC4533E0}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.33199074074074075</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>4.7291666666666669E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="15" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="16" t="s">
+      <c r="B7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1">
-      <c r="A9" s="16" t="s">
+      <c r="B9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1008,7 +2296,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
@@ -1016,101 +2304,93 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="25">
+        <v>5.3530092592592594E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="4" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="B8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1123,8 +2403,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
@@ -1132,100 +2412,85 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="4" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="B2" s="25">
+        <v>6.0578703703703704E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="15" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="B7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>38</v>
+      <c r="B8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1239,8 +2504,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
@@ -1248,100 +2513,85 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="4" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="B2" s="25">
+        <v>6.8912037037037036E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="15" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="B7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>38</v>
+      <c r="B8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1356,7 +2606,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
@@ -1364,100 +2614,100 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="4" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="B2" s="25">
+        <v>0.11116898148148148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="B6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="15" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="B7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>38</v>
+      <c r="B9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1470,9 +2720,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F255CBDC-D79F-4664-A601-039EFB7C45DD}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
@@ -1480,100 +2730,388 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50.1" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:5" ht="21.95" customHeight="1">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="4" spans="1:5" ht="8.1" customHeight="1"/>
-    <row r="5" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="B2" s="25">
+        <v>0.11950231481481481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="15" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="B7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="B9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E03924-F234-454D-B4DD-8BF9A6D4D073}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.14049768518518518</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="B8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>4</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2E2DAB-2F43-4F4D-B996-F0703D78035B}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0.15972222222222221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>38</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>4</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
